--- a/results/Int All Data 0.2/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.2/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001284608398329199</v>
+        <v>9.115929665713933e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005833700967857579</v>
+        <v>0.0003798277649875981</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003846905269815891</v>
+        <v>-0.0001780789257510185</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.406506917223441e-05</v>
+        <v>-0.000103188928306609</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002293970887192609</v>
+        <v>-0.0008145807761126146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001607240993621322</v>
+        <v>0.00160617361673382</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004334123404762747</v>
+        <v>-0.000400073116189652</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002304090007057578</v>
+        <v>-0.0004307139765376722</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0005016544154346647</v>
+        <v>-0.0004621683139422282</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000108620381682677</v>
+        <v>-0.0002642760146009782</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002185187833003899</v>
+        <v>-0.0001070177344369882</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002214207459136686</v>
+        <v>-0.0001742686155394346</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008820314073652002</v>
+        <v>-0.0002730119710232349</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001440467644420833</v>
+        <v>0.0002123276215037218</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0004054641699606154</v>
+        <v>0.0004322775262316835</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003646392647685858</v>
+        <v>0.001022278813015581</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001755355642871182</v>
+        <v>-0.0005513897254700972</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007294452190782463</v>
+        <v>-0.0008197296702104362</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001483835846115034</v>
+        <v>-0.0006317116618625785</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0007521797298970268</v>
+        <v>-0.0007462679175131149</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004233699787421463</v>
+        <v>-0.0001056487887198753</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005573454919213848</v>
+        <v>0.000636305326936909</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004073127664428754</v>
+        <v>-0.0007037116888593376</v>
       </c>
       <c r="Y3" t="n">
-        <v>-5.663468283727529e-06</v>
+        <v>-0.0001495366011445598</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001838140521348345</v>
+        <v>0.001794683650320194</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001983883566593338</v>
+        <v>0.0005304435304587486</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002451064170402462</v>
+        <v>0.0002075546147002827</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0003148919379684467</v>
+        <v>0.0004050741104031387</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0009668558408534922</v>
+        <v>0.001933795143693819</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.001610129307869864</v>
+        <v>6.23208362329045e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0006588924723040761</v>
+        <v>3.698143996974241e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0005903251843999323</v>
+        <v>3.192747325521667e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.709815015356401e-05</v>
+        <v>6.155366298484676e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0005246846026337005</v>
+        <v>0.0002253659939099982</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001493687173520066</v>
+        <v>-0.001802205399970259</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0116961027852585</v>
+        <v>0.008231327258519754</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0005158778560778821</v>
+        <v>-0.0004628540677035297</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003184265117137396</v>
+        <v>0.001054380385527009</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001481746905050457</v>
+        <v>0.001014406231783813</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001538860053402113</v>
+        <v>-0.0003988586685490647</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.000197852145475309</v>
+        <v>-0.0006058673328043563</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0003014424792954006</v>
+        <v>-9.303096472681018e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.784990791011375e-06</v>
+        <v>-0.001741442215118854</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0002176883515946382</v>
+        <v>0.000303172235818766</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0006931482414265844</v>
+        <v>-0.0006070682611008293</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.001582722220668559</v>
+        <v>-0.0002838701993828641</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0006353682528808481</v>
+        <v>0.00100860946822364</v>
       </c>
       <c r="AW3" t="n">
-        <v>-6.885867917037268e-05</v>
+        <v>0.0004112584483973236</v>
       </c>
       <c r="AX3" t="n">
-        <v>-9.338619269486316e-05</v>
+        <v>-0.0001257160569800331</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0004789239030413206</v>
+        <v>0.000330309977122778</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.003537646927406196</v>
+        <v>-0.0007362525227394735</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.006718312991089988</v>
+        <v>0.002631319155185991</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002854869237116611</v>
+        <v>0.005918890473901723</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.637075402337265e-05</v>
+        <v>-0.0001188144802975355</v>
       </c>
       <c r="BD3" t="n">
-        <v>-4.598525028680522e-05</v>
+        <v>-0.0002555404248479487</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0007513463854374291</v>
+        <v>-0.0008221655118455983</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.004392033582887146</v>
+        <v>0.0003915362022810342</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.002111006253894393</v>
+        <v>0.001985932651757394</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.664899845495901e-05</v>
+        <v>0.0004658508270350803</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.004286374762605977</v>
+        <v>0.003690077226815779</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0006727707836934372</v>
+        <v>0.001224054600398052</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.001212098288559056</v>
+        <v>-0.001131882248197671</v>
       </c>
       <c r="BL3" t="n">
-        <v>9.376254843711071e-05</v>
+        <v>-0.0001587954316689499</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.000515315214124078</v>
+        <v>-0.001511256255773483</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.005804148210881774</v>
+        <v>0.003671139725541461</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0007938284304992683</v>
+        <v>-5.214076937457642e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0007909928582669923</v>
+        <v>-0.0007116825150188422</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0005753921806619991</v>
+        <v>0.002131889396369884</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.000919802782042689</v>
+        <v>-0.001026028345092945</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0008060325468565719</v>
+        <v>0.0009036587474891245</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0009656654278777344</v>
+        <v>-0.0008159941042773713</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0002406681882034199</v>
+        <v>-0.001192044049377822</v>
       </c>
       <c r="BW3" t="n">
-        <v>-7.779395774242248e-06</v>
+        <v>-9.015751168912512e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0002036303589322385</v>
+        <v>-0.0009280009185797077</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.002389074555549063</v>
+        <v>0.0004175253494352584</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0001244592528257206</v>
+        <v>-0.0007515636145504624</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.000198730515317036</v>
+        <v>0.0001522048557052825</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0006111796896195342</v>
+        <v>-0.000215924806712109</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0001184414483785856</v>
+        <v>-0.0006481931849331435</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0006378454788916009</v>
+        <v>-8.10013379653496e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0004250589062236599</v>
+        <v>-0.0008082162988898789</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.00193367809296157</v>
+        <v>-0.0009122163409824257</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0001631941533487159</v>
+        <v>0.0008946467774763866</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.001726185014944426</v>
+        <v>0.0002271172324364235</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0009792720823089619</v>
+        <v>0.0001854648152293371</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.833521390310789e-05</v>
+        <v>2.486893547994473e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>6.827278190222547e-05</v>
+        <v>0.0002346696624892119</v>
       </c>
       <c r="CL3" t="n">
-        <v>5.872839126391915e-05</v>
+        <v>0.001089906563218465</v>
       </c>
       <c r="CM3" t="n">
-        <v>-5.732997370347713e-05</v>
+        <v>0.0002380997639415194</v>
       </c>
       <c r="CN3" t="n">
-        <v>3.32354057116313e-05</v>
+        <v>0.0003464636249163666</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0001592937605369682</v>
+        <v>8.722435724182854e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>6.987971826621808e-05</v>
+        <v>3.395072453108105e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.001038687660699044</v>
+        <v>-0.000406645253063751</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.002043387924666685</v>
+        <v>7.290844019173682e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0004115779315577994</v>
+        <v>-0.0005347992709955052</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0002529555492069735</v>
+        <v>0.0003496875383531395</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.0001684175190807579</v>
+        <v>-0.0001015102542882707</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001869272284595525</v>
+        <v>-5.280094458986804e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0002410784885803185</v>
+        <v>-0.0004419311579638719</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0006425992574177041</v>
+        <v>-0.0001384766623360234</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0002671618102154239</v>
+        <v>-0.000192243173003197</v>
       </c>
       <c r="DA3" t="n">
-        <v>3.052262313430586e-05</v>
+        <v>-0.0002766406821609024</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0001552344530449468</v>
+        <v>0.0006176607288398185</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0001912265315592431</v>
+        <v>-0.0002426131205468984</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0003098136713073895</v>
+        <v>8.430639372970061e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>7.512292411321448e-05</v>
+        <v>0.0002015602584491761</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0005090633846898696</v>
+        <v>0.0004505380437298445</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.00135287299070543</v>
+        <v>-0.0001980838833611687</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001102566458821444</v>
+        <v>-0.0003450557686233402</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0008802272421923019</v>
+        <v>0.0002282817505874557</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0005975925403928639</v>
+        <v>0.000242531226377074</v>
       </c>
       <c r="DK3" t="n">
-        <v>-1.740048580330274e-05</v>
+        <v>-0.0007821042987264815</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001952156601617716</v>
+        <v>-4.228277314667572e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.001483179406517641</v>
+        <v>-0.0008914696684531132</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001625058748612844</v>
+        <v>-0.002374077453451091</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001316438872815037</v>
+        <v>-0.0005879663602987907</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0002255903348838628</v>
+        <v>-0.00199413446523976</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.0001330117877279924</v>
+        <v>4.44648184020291e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-9.761689839110186e-05</v>
+        <v>4.888137935216475e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.0003086595253402558</v>
+        <v>-0.0002034644201347746</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0006609489074835406</v>
+        <v>-0.001025646165391206</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001731529152779188</v>
+        <v>-0.001667663378312094</v>
       </c>
       <c r="DV3" t="n">
-        <v>-3.868471953578644e-06</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0001697985087406184</v>
+        <v>-4.775497792767091e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.258551690892511e-05</v>
+        <v>0.0003307097384526613</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001206657699950518</v>
+        <v>0.001089967757266759</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.260796193667147e-05</v>
+        <v>-8.570013119366892e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.000558937522302695</v>
+        <v>-0.001071007333824723</v>
       </c>
       <c r="EB3" t="n">
-        <v>-4.282597914305299e-05</v>
+        <v>7.41420255854442e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0006150012390002092</v>
+        <v>-3.723859517993589e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>7.36114026205059e-05</v>
+        <v>6.499242512697845e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>3.868471953578644e-06</v>
+        <v>6.963986215434369e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0003240550067174353</v>
+        <v>-0.0006508878678765117</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0004593515210492948</v>
+        <v>-0.000149103755919916</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.000108571259218081</v>
+        <v>-0.0002565531850385982</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0001787363215248305</v>
+        <v>-0.0007829396912317354</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0002333800885645853</v>
+        <v>-0.0002694251792242397</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.000670394019356424</v>
+        <v>-0.0004538381492615074</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.052343419000404e-05</v>
+        <v>1.611020979164215e-07</v>
       </c>
       <c r="EM3" t="n">
-        <v>-1.510126998104266e-05</v>
+        <v>0.0001210358618516572</v>
       </c>
       <c r="EN3" t="n">
-        <v>8.582803266327655e-05</v>
+        <v>0.0001024335532537346</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>4.840665191034654e-05</v>
+        <v>2.920916639879256e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0006062855717131421</v>
+        <v>-0.0007305237914493202</v>
       </c>
       <c r="ER3" t="n">
-        <v>-3.998400639744215e-06</v>
+        <v>0.0002449962279225171</v>
       </c>
       <c r="ES3" t="n">
-        <v>8.460925736428093e-05</v>
+        <v>-8.543437004777e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0009249174767661827</v>
+        <v>-0.0009687536992908585</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0004016383263412262</v>
+        <v>-0.0004839216959885452</v>
       </c>
       <c r="EV3" t="n">
-        <v>3.00876181866605e-05</v>
+        <v>6.579796893706693e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0004876079160379332</v>
+        <v>-0.0009224343838791383</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0002282833490420433</v>
+        <v>-2.17371811551092e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0007638839636107942</v>
+        <v>-0.000519546990570402</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003404973845362594</v>
+        <v>0.002299727142824599</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008630184218324083</v>
+        <v>0.0006051179307597741</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001183510266561826</v>
+        <v>0.001002322822474629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00139697062608421</v>
+        <v>0.001208545983311855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007902815872950007</v>
+        <v>0.0007558287696897126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00261593005263508</v>
+        <v>0.003473514845308503</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008980704708774078</v>
+        <v>0.001243144099025341</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002940585423121632</v>
+        <v>0.003116185975309593</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002591113356417982</v>
+        <v>0.001856883697819159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005646203510666709</v>
+        <v>0.0008140685288409873</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005766854187746117</v>
+        <v>0.0007983805586231081</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001338304218898653</v>
+        <v>0.001432062415083673</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004625217936405032</v>
+        <v>0.005435649756204987</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002843137569491628</v>
+        <v>0.002105563464300148</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001241538395004551</v>
+        <v>0.001694710651963845</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009086981389692448</v>
+        <v>0.00803983581508411</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001757317122340055</v>
+        <v>0.00149725401511865</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001868223616541003</v>
+        <v>0.001840874021250409</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000400312503842506</v>
+        <v>0.001288393384775089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002140133275632491</v>
+        <v>0.001767101638158741</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00241553230518736</v>
+        <v>0.0029338521788694</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002520507756138671</v>
+        <v>0.002108388032385793</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004961284298035586</v>
+        <v>0.004962256961382903</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008686362098454414</v>
+        <v>0.0004063475428909816</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004023222094329207</v>
+        <v>0.004279267703700211</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004794568820619462</v>
+        <v>0.002734017678102328</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000895509946461197</v>
+        <v>0.001216079400501179</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001335775193348578</v>
+        <v>0.001201561527564889</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004904423701521587</v>
+        <v>0.006346142592797008</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01260008747732344</v>
+        <v>0.01882976047175844</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003806959146800131</v>
+        <v>0.005724352236786243</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001915506275978561</v>
+        <v>0.00191146148022985</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.002555288045734328</v>
+        <v>0.0009799959648857267</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002461787912749982</v>
+        <v>0.006311044947416934</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007705418608483465</v>
+        <v>0.01080980202077594</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01384291607803631</v>
+        <v>0.01418116553652718</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001416443783463587</v>
+        <v>0.001968530444480576</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005726717568896907</v>
+        <v>0.005064969445508861</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003086104607108986</v>
+        <v>0.003483599524058736</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.006394606721427663</v>
+        <v>0.006554959943179881</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001205071944440931</v>
+        <v>0.002087129491438436</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002975453972601322</v>
+        <v>0.001838858413486697</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01746101789917277</v>
+        <v>0.01613033710201402</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001365851140447047</v>
+        <v>0.001967735459897044</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002490796269234237</v>
+        <v>0.002656996207755392</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002585352179506701</v>
+        <v>0.00159826427851067</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002489156774037495</v>
+        <v>0.001796900860907613</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002238314311556303</v>
+        <v>0.001499279798802476</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007212753609062116</v>
+        <v>0.0004919309267697418</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001372835947365888</v>
+        <v>0.002688231843687214</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.008339870389766836</v>
+        <v>0.003343182064315598</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01275253772822572</v>
+        <v>0.008722142923865344</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005882625634230892</v>
+        <v>0.01223970350595659</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005141068202491686</v>
+        <v>0.0007396019576343333</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000693339075453792</v>
+        <v>0.0005664666540263892</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002409674581972757</v>
+        <v>0.003474498469640871</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.009743815965740607</v>
+        <v>0.007869164525669456</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004159739426849099</v>
+        <v>0.004223755764943413</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006420992161516153</v>
+        <v>0.001232571241007151</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.009655693858404974</v>
+        <v>0.01079409423457395</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001467998610328309</v>
+        <v>0.002307794533477433</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002349209131734067</v>
+        <v>0.002391392484606355</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001461549945636701</v>
+        <v>0.001134713943787376</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001848478659593245</v>
+        <v>0.001819495896624306</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01155101960901755</v>
+        <v>0.01320522929433621</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002243312388531918</v>
+        <v>0.004075824544565685</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002974931192520068</v>
+        <v>0.001081151458433213</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004278703450886057</v>
+        <v>0.004908405865236649</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004662087433670275</v>
+        <v>0.004381134892283367</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002253134442994162</v>
+        <v>0.001281856319081458</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.004183887501588947</v>
+        <v>0.002135546644301052</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003269288778385112</v>
+        <v>0.002767136673116744</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.550358920145031e-05</v>
+        <v>0.0002109368976426108</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.00258292602479019</v>
+        <v>0.001277206254697695</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004570988908092403</v>
+        <v>0.008753937810106627</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.006773197693631008</v>
+        <v>0.003184556550052742</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001931114451296999</v>
+        <v>0.001395331700452923</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002009516499563068</v>
+        <v>0.002706278527029067</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004422859324313663</v>
+        <v>0.001298702676019569</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.008373172682717525</v>
+        <v>0.003868074579706971</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003496781129295989</v>
+        <v>0.00199479109589492</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003597482875036641</v>
+        <v>0.00243328610252294</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001973512427831571</v>
+        <v>0.001692805538409634</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002604321763954356</v>
+        <v>0.0009919933366402758</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005703298500715014</v>
+        <v>0.003131270028928095</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001191022476517076</v>
+        <v>5.905037309056942e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001964132440327673</v>
+        <v>0.001109569340282001</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.002855382359796812</v>
+        <v>0.002821163828464638</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001657679349080632</v>
+        <v>0.0008792359944694996</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000804352973729896</v>
+        <v>0.0006389501307952369</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001376759607306654</v>
+        <v>0.001054896212805129</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0003483079691738064</v>
+        <v>0.0001488644255366295</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003326430178161525</v>
+        <v>0.002086222088869711</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003269970007865369</v>
+        <v>0.00185138358227778</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.004365198593524146</v>
+        <v>0.001890906992517925</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002949271210823685</v>
+        <v>0.001154716770543626</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001664562759148744</v>
+        <v>0.0004782376179426075</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.000851301647696925</v>
+        <v>0.0005545590182902852</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002430763777804022</v>
+        <v>0.001759004950785852</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.003289891999540499</v>
+        <v>0.001478488482873135</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001011191991362273</v>
+        <v>0.0003014404578180392</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0005791407761192293</v>
+        <v>0.0005317935829273733</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001314878652723011</v>
+        <v>0.001523242955690774</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001906435557613446</v>
+        <v>0.001266391102331378</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.000542381125109729</v>
+        <v>0.0003651687693841161</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001385238074334103</v>
+        <v>0.001029266195676192</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001864042052876997</v>
+        <v>0.0008359165902856661</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.006154999249880425</v>
+        <v>0.001116260733240697</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.007513432142737875</v>
+        <v>0.00224781699466476</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.00269079529158271</v>
+        <v>0.001331954973837073</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002743737428156034</v>
+        <v>0.001253163580230053</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.00139366356763347</v>
+        <v>0.000956168327563624</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0003034914607689867</v>
+        <v>0.0003477204663910483</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001800778746339776</v>
+        <v>0.002055678226576218</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003102560800718333</v>
+        <v>0.004964884109368694</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001614593363186114</v>
+        <v>0.003715947399244041</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002775746089400803</v>
+        <v>0.003180472226867709</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.000309192425166734</v>
+        <v>6.884848166830844e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0002969955607448204</v>
+        <v>0.0003176857045581435</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0008334790506458427</v>
+        <v>0.0007353145043790661</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001676070285346596</v>
+        <v>0.002517457974260827</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.004135829344703926</v>
+        <v>0.004747696457682118</v>
       </c>
       <c r="DV4" t="n">
-        <v>1.223318243778967e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.00075320336645439</v>
+        <v>0.0001665489146640833</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000746518876583426</v>
+        <v>0.002652000890438082</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.004625905753409503</v>
+        <v>0.002136995922464746</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003515676704126108</v>
+        <v>0.0002713488696598953</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002774052775661259</v>
+        <v>0.001820857880779098</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.004040551113951453</v>
+        <v>0.002819787786442001</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003549532790419827</v>
+        <v>0.0003350600554886469</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00138424794083001</v>
+        <v>0.00090611666927837</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.223318243778967e-05</v>
+        <v>0.0001941051207699087</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001367865839470557</v>
+        <v>0.001003187700306871</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.002195970106596121</v>
+        <v>0.0007257563785298281</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004316100074002776</v>
+        <v>0.0008244383917362604</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.00170591983863826</v>
+        <v>0.001147564815299561</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001691421436985869</v>
+        <v>0.001401938338975286</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001803126848143842</v>
+        <v>0.0008510368837674116</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001739622695530101</v>
+        <v>1.847204265502268e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002441920375787416</v>
+        <v>0.0002168331699219329</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004097694493619633</v>
+        <v>0.0004613433688017031</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0002432131161186216</v>
+        <v>0.0001742797786314721</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.002248634660195173</v>
+        <v>0.001609261586225034</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.264405301946609e-05</v>
+        <v>0.0007189039614539296</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001378714495622901</v>
+        <v>0.0003475991271176363</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001535166929652077</v>
+        <v>0.001172071843458608</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.002951323178174803</v>
+        <v>0.001296018036889016</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0001853259050197294</v>
+        <v>0.0002171965027694134</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0009086962007073644</v>
+        <v>0.001835266965639903</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001895220010904192</v>
+        <v>0.001845358284046141</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0008784377790218203</v>
+        <v>0.001067570399111006</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004857621440536031</v>
+        <v>-0.004229480737018443</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0003915426781519127</v>
+        <v>-0.0006242197253432891</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001199226305609302</v>
+        <v>-0.001968998743192296</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002475822050290155</v>
+        <v>-0.001866251944012409</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.000670297444490997</v>
+        <v>-0.002507076425394228</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001801096319498829</v>
+        <v>-0.00295188030731901</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0006656225528582805</v>
+        <v>-0.002992317023857627</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001633165829145744</v>
+        <v>-0.00613967766692246</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006331542594013795</v>
+        <v>-0.003990790483499596</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001074443591711405</v>
+        <v>-0.002021772939346789</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0003094777562862916</v>
+        <v>-0.002079168332666992</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001360808709175709</v>
+        <v>-0.003760552570990028</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007157137145141978</v>
+        <v>-0.009476209516193568</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.001644479248238073</v>
+        <v>-0.001996867658574819</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002973199329983267</v>
+        <v>-0.001252936570086183</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.006072026800670038</v>
+        <v>-0.00757386600083223</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00155520995334365</v>
+        <v>-0.002604976671850701</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.002345058626465701</v>
+        <v>-0.00485240598463399</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0004398240703718637</v>
+        <v>-0.003878448620551811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.004860031104199048</v>
+        <v>-0.00381231671554253</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.003433835845896161</v>
+        <v>-0.003878448620551833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004150352388410339</v>
+        <v>-0.002597402597402576</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008169250104733983</v>
+        <v>-0.007440355843105473</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001507537688442217</v>
+        <v>-0.001132228063081264</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.005862646566164165</v>
+        <v>-0.003460342146189732</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.003597678916827873</v>
+        <v>-0.003914044512663073</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0007830853563038587</v>
+        <v>-0.002760497667185047</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.001424382069543362</v>
+        <v>-0.0009788566953798262</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.008919597989949768</v>
+        <v>-0.00716080402010053</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02494945410432672</v>
+        <v>-0.05127375657096639</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.006308127780024287</v>
+        <v>-0.01564900930044473</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.00548576214405363</v>
+        <v>-0.00319450060655071</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.003894472361809054</v>
+        <v>-0.0009571369121930684</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.002304892842701145</v>
+        <v>-0.01267496111975116</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01370804690659116</v>
+        <v>-0.03016579053780828</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.014070351758794</v>
+        <v>-0.01695979899497491</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001717637201508204</v>
+        <v>-0.004448038819247824</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.006216423637758994</v>
+        <v>-0.00602455871066766</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.003520309477756312</v>
+        <v>-0.001594090202177267</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.009631490787269714</v>
+        <v>-0.01302488335925349</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001663442940038706</v>
+        <v>-0.00528771384136858</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.006769825918762106</v>
+        <v>-0.003760552570990006</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.04023453295592398</v>
+        <v>-0.04383340072786085</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003841488071168575</v>
+        <v>-0.002102709260008062</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.006783919597989962</v>
+        <v>-0.005482115085536532</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.008085462924172605</v>
+        <v>-0.003801051354629958</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.005194805194805219</v>
+        <v>-0.001135473766640593</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.003477167993297048</v>
+        <v>-0.002639296187683282</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001842546063651618</v>
+        <v>-0.00105135463000402</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.001895551257253414</v>
+        <v>-0.003852596314907919</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.001018010963195004</v>
+        <v>-0.005015552099533427</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.006367825722664433</v>
+        <v>-0.009196321471411483</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.008420611646418108</v>
+        <v>-0.005278592375366553</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0009284332688588304</v>
+        <v>-0.0007870753935376839</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001818181818181852</v>
+        <v>-0.001759296281487455</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.004983249581239568</v>
+        <v>-0.006597361055577821</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.005488060326769994</v>
+        <v>-0.011646418098031</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.003300076745970804</v>
+        <v>-0.001165210153974161</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.0008123791102514599</v>
+        <v>-0.00141528507885158</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.0103223330775134</v>
+        <v>-0.009363008442056764</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001926298157453943</v>
+        <v>-0.001599360255897686</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.00129397492923573</v>
+        <v>-0.005948889819857561</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002282398452611245</v>
+        <v>-0.00143856920684291</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.001900525677314979</v>
+        <v>-0.004245855236554741</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.00812735651445331</v>
+        <v>-0.00655737704918039</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.00237169517884912</v>
+        <v>-0.00839813374805597</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.008820116054158644</v>
+        <v>-0.00278529980657638</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.00602507076425397</v>
+        <v>-0.003275374039627943</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.004874274661508737</v>
+        <v>-0.01164577436312169</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.005569514237855988</v>
+        <v>-0.0002021835826930385</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.006712494945410452</v>
+        <v>-0.006186817630408336</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004526112185686682</v>
+        <v>-0.007074490220557594</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0001248439450686423</v>
+        <v>-0.0006065507480792487</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.005764023210831748</v>
+        <v>-0.003771384136858469</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.005372217958557135</v>
+        <v>-0.01013046815042208</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.01243718592964827</v>
+        <v>-0.00632328308207708</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.003801051354629958</v>
+        <v>-0.001399440223910475</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002413649604660817</v>
+        <v>-0.00436716538617059</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.008704061895551285</v>
+        <v>-0.002488335925349916</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.007199334165626292</v>
+        <v>-0.004393468118195953</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.006073500967118018</v>
+        <v>-0.004577611319184316</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.0009284332688588193</v>
+        <v>-0.007238172260412378</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003601340033500855</v>
+        <v>-0.002119152339064434</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002166344294003908</v>
+        <v>-0.001166407465007757</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.003791102514506783</v>
+        <v>-0.005701577031944937</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-4.189359028068384e-05</v>
+        <v>-3.837298541826683e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002911443590780394</v>
+        <v>-0.001719312275090013</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.006259720062208351</v>
+        <v>-0.004082426127527206</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.003685092127303202</v>
+        <v>-0.0005755947812739693</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001237911025145078</v>
+        <v>-0.0002931323283082321</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.002371695178849109</v>
+        <v>-0.00186625194401242</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0006700167504187782</v>
+        <v>-0.0002513615416841031</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.005234505862646577</v>
+        <v>-0.004743390357698274</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.001710730948678041</v>
+        <v>-0.003499222395023305</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.009825918762089002</v>
+        <v>-0.003365570599613121</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.00692456479690523</v>
+        <v>-0.001290054099042848</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0004187604690117586</v>
+        <v>-0.001051354630004031</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0005256773150020156</v>
+        <v>-0.0006576402321082586</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.004912959381044501</v>
+        <v>-0.003558994197292042</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.004587869362363906</v>
+        <v>-0.002598960415833729</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.001005802707930403</v>
+        <v>-0.0008396641343462851</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.000618955512572561</v>
+        <v>-0.00165790537808328</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.0028974158183242</v>
+        <v>-0.001319472211115591</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.005415860735009692</v>
+        <v>-0.002340752110514166</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0001151189562548005</v>
+        <v>-0.0005054432348366889</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.002243713733075481</v>
+        <v>-0.0009212730318258089</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004061895551257277</v>
+        <v>-0.0009300444803881814</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.002707930367504874</v>
+        <v>-0.002871006874241777</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01558994197292074</v>
+        <v>-0.004160186625194384</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.004061895551257277</v>
+        <v>-0.001879248300679781</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.002911443590780394</v>
+        <v>-0.001414898044111501</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.001527016444792506</v>
+        <v>-0.002110514198004576</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>-0.0003888024883359487</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.005647969052224399</v>
+        <v>-0.006105944197331103</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.007969052224371397</v>
+        <v>-0.01391023048928423</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.00294003868471957</v>
+        <v>-0.00473109583501814</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.004487427466150895</v>
+        <v>-0.008665377176015432</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0006576402321083585</v>
+        <v>-3.868471953574204e-05</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.000586264656616442</v>
+        <v>-0.0005443234836702837</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.001005802707930392</v>
+        <v>-0.002122347066167274</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.003643216080402012</v>
+        <v>-0.007466150870406152</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.01203094777562865</v>
+        <v>-0.01124140719773552</v>
       </c>
       <c r="DV5" t="n">
-        <v>-3.868471953578645e-05</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.001759530791788866</v>
+        <v>-0.0004448038819247602</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0007278608976950985</v>
+        <v>-0.004124545086938891</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01234042553191489</v>
+        <v>-0.001555209953343695</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0004306969459671129</v>
+        <v>-0.0006469874646178542</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.004990328820116086</v>
+        <v>-0.004326728669631974</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.006108065779169958</v>
+        <v>-0.00379110251450675</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.003907156673114143</v>
+        <v>-0.0005409904286308387</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.001611665387567107</v>
+        <v>-0.001199226305609258</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-4.187604690117919e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001633165829145755</v>
+        <v>-0.003404255319148919</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0023031825795645</v>
+        <v>-0.001624758220502876</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0003350083752094113</v>
+        <v>-0.002449455676516332</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.001547388781431358</v>
+        <v>-0.001959216313474665</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002359767891682807</v>
+        <v>-0.002183582693085295</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.005653266331658302</v>
+        <v>-0.001799280287884897</v>
       </c>
       <c r="EL5" t="n">
-        <v>-3.915426781518905e-05</v>
+        <v>-3.837298541826683e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0004993757802746023</v>
+        <v>-0.0002485501242750265</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0005415860735009992</v>
+        <v>-0.0005446166736489233</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0001534919416730673</v>
+        <v>-0.0001547388781431014</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.006150870406189568</v>
+        <v>-0.004855129209083831</v>
       </c>
       <c r="ER5" t="n">
-        <v>-3.998400639744215e-05</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-3.868471953578645e-05</v>
+        <v>-0.0006242197253433001</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.003752417794971019</v>
+        <v>-0.002628386575010078</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.005918762088974872</v>
+        <v>-0.002668823291548694</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0003234937323089326</v>
+        <v>-0.0002021835826930829</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.002261306532663354</v>
+        <v>-0.004541895066562285</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.004933437744714187</v>
+        <v>-0.002177293934681157</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.002346041055718495</v>
+        <v>-0.002647735993860301</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-8.819110318996071e-05</v>
+        <v>-0.001624312544010534</v>
       </c>
       <c r="C6" t="n">
-        <v>1.04036620890563e-05</v>
+        <v>-2.095958639969919e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000203310059444764</v>
+        <v>-0.0005870516770750651</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001098298524803579</v>
+        <v>-0.001019464070905537</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.00014346155484668</v>
+        <v>-0.00100563988070447</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0005026821085981682</v>
+        <v>-0.0003316256787943839</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0002350129042482995</v>
+        <v>-0.0007525550747706667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005051317082923473</v>
+        <v>-0.001734228966022278</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.00163282755950426</v>
+        <v>-0.001751761606915045</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.355289577730851e-05</v>
+        <v>-0.0005274068473063138</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.281407035177989e-05</v>
+        <v>-0.0002029032478743559</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0006216567356805231</v>
+        <v>-0.0004433710225486526</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0004569966752533877</v>
+        <v>-0.003762464792625162</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0009066671591512809</v>
+        <v>-0.001112088488865987</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.000958114980800387</v>
+        <v>-0.000602660138431918</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0008365526146628721</v>
+        <v>-0.005035961992244223</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001020953594349735</v>
+        <v>-0.001387363870117556</v>
       </c>
       <c r="S6" t="n">
-        <v>4.266621983578468e-07</v>
+        <v>-0.001137901220262202</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.117794466904079e-05</v>
+        <v>-0.0009133919112001038</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0009593957388031372</v>
+        <v>-0.001571556883871208</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001002902608944015</v>
+        <v>-0.002164416824837431</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.000614272498038243</v>
+        <v>-0.0007159264709103386</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002436788660774031</v>
+        <v>-0.003261795761528447</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.000259485252749575</v>
+        <v>-0.0002264201854181691</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001484767482598515</v>
+        <v>-0.0002066565339943455</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.817157818383762e-06</v>
+        <v>-0.0009193256825951318</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0004785674174830001</v>
+        <v>3.142019271049623e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0002698292542279823</v>
+        <v>-0.000257465365138107</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0004019104868409396</v>
+        <v>-0.0007772715932813617</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0009830790408625804</v>
+        <v>0.001780038593839237</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.002184076971435483</v>
+        <v>0.0002829293451013098</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0005372948706187236</v>
+        <v>-0.000971073751326315</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0009158725829205239</v>
+        <v>-0.0003661059262673766</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0007366389812665852</v>
+        <v>-0.001233073724308276</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001837584775576342</v>
+        <v>-0.002146672083990853</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.002826844738007428</v>
+        <v>-0.001554732528952785</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.824543757297963e-05</v>
+        <v>-0.001479795217276708</v>
       </c>
       <c r="AM6" t="n">
-        <v>-6.742141928648418e-05</v>
+        <v>-0.002010128670819747</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001751666339873753</v>
+        <v>-0.0003160725836432066</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0001574791793198388</v>
+        <v>-0.00270128133335299</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0005025125628141003</v>
+        <v>-0.0008677234734381812</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0001778972698413622</v>
+        <v>-0.001392161047653737</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.002071994580573883</v>
+        <v>-0.002650644421332979</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0002603704941508161</v>
+        <v>-0.001042254171426299</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0006826765821354274</v>
+        <v>-0.0008813528393681353</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.002528430390982259</v>
+        <v>-0.0005011594842480926</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001270030937100489</v>
+        <v>-0.0002175926308607606</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001127375191593363</v>
+        <v>-0.0003439591666216907</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.000303171556586132</v>
+        <v>-0.0003228171952391973</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0002096698754414733</v>
+        <v>-0.0009918684770909266</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0004649507222794697</v>
+        <v>-0.002423401926719318</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0003002099237051165</v>
+        <v>-0.0008075433971495267</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0003253146138178204</v>
+        <v>0.001278471954440222</v>
       </c>
       <c r="BC6" t="n">
-        <v>-7.008518873083402e-05</v>
+        <v>-0.0004579141202370074</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001516376870198122</v>
+        <v>-0.0002258625138016196</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.236698785082705e-05</v>
+        <v>-0.002197512217768008</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0001557704898702411</v>
+        <v>-0.0007345372469612864</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0004922540716429697</v>
+        <v>-0.0003424096924216219</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.000365851627649455</v>
+        <v>-0.0003043052177359978</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0008347722084699444</v>
+        <v>-0.002094169807181115</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0002556381172474226</v>
+        <v>-0.0004550371932752179</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0004182874588858132</v>
+        <v>-0.002698338759967117</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005784085212883926</v>
+        <v>-0.0008748962116770481</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0003506114609887534</v>
+        <v>-0.003040782011451879</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00152614596249325</v>
+        <v>-0.002847994018010805</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.000629260805431056</v>
+        <v>-0.001159600862574453</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0006245031712405952</v>
+        <v>-0.001232781372946837</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.002274957627054486</v>
+        <v>-0.0002729444982577156</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0008414320556096311</v>
+        <v>-0.001671641397163293</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.001490466577110169</v>
+        <v>-1.936969926206178e-05</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.99760095961216e-05</v>
+        <v>-0.001034653420356293</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0001413021528145791</v>
+        <v>-0.001379325634677467</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.00100080873433076</v>
+        <v>-0.001445063613632416</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0006830830206722594</v>
+        <v>-0.002291752958676208</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001498620991340024</v>
+        <v>-0.002980350453832273</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0003004426722858</v>
+        <v>-0.000382475116754008</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0009704811969267978</v>
+        <v>-0.001245381924599587</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001351290389443457</v>
+        <v>-0.001367663584527062</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.002654246609785704</v>
+        <v>-0.002678968452284944</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002736364237522085</v>
+        <v>-0.002128386492323309</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.000260919889380809</v>
+        <v>-0.001488264736161907</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0002107449634874747</v>
+        <v>-3.174530481739879e-05</v>
       </c>
       <c r="CH6" t="n">
-        <v>-1.080760736321684e-06</v>
+        <v>-0.0005859693100254664</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001524892304963032</v>
+        <v>-0.000747644841277681</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0008956254201274161</v>
+        <v>-0.0004756255714156582</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0001726784343822119</v>
+        <v>-0.0006381330813799046</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0004217381175955742</v>
+        <v>-0.0002506586873318478</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0005909939319770019</v>
+        <v>-8.748055987558011e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.001266633182413621</v>
+        <v>-0.0005658669554971324</v>
       </c>
       <c r="CP6" t="n">
-        <v>-2.901353965183983e-05</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.003119426752837795</v>
+        <v>-0.000793090284991152</v>
       </c>
       <c r="CR6" t="n">
-        <v>-6.104865389347514e-05</v>
+        <v>-0.0006287457146963327</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.001066413660472462</v>
+        <v>-0.001648607624838461</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001149839759040797</v>
+        <v>6.105677033245438e-05</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.000309722167908541</v>
+        <v>-0.0003454382845046317</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0002999239634721956</v>
+        <v>-0.0003606230252603815</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0006856835790576832</v>
+        <v>-0.001753112432381745</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.000625125888290648</v>
+        <v>-0.001116140626446052</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0</v>
+        <v>-0.0002245501045881226</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0002624416796267071</v>
+        <v>-0.0002404605215005656</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0003873606078563935</v>
+        <v>-0.0002722596544938616</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.000222433810237252</v>
+        <v>-0.001071120278132168</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001600492031250706</v>
+        <v>-0.0005019322227432898</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0003269333848788303</v>
+        <v>-8.194733705516044e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.00116428513278955</v>
+        <v>-0.0005979202913341336</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.00427438403577591</v>
+        <v>-0.001302004860474676</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001012917988839485</v>
+        <v>0.0001256412982381327</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.000402693687402278</v>
+        <v>-0.0005354939831520883</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0006868736184051482</v>
+        <v>-0.001353181507966358</v>
       </c>
       <c r="DL6" t="n">
-        <v>9.671179883946612e-06</v>
+        <v>-0.0002699213569704012</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.002397831250876306</v>
+        <v>-0.0009941160252638914</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.002729872144548548</v>
+        <v>-0.004657456541390209</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.002711703659683778</v>
+        <v>-0.003030501066386693</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001153852695478386</v>
+        <v>-0.003552658314902693</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0003076179626152808</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0003020752638220825</v>
+        <v>-5.997600959616322e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-3.883136650913166e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.001836474473470392</v>
+        <v>-0.001303663547652093</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0012520669047383</v>
+        <v>-0.004484839575051261</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0004471597455599774</v>
+        <v>-0.0001072835952933421</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0004270087820589436</v>
+        <v>-0.0006521347296528729</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002309954855878657</v>
+        <v>6.105677033247104e-05</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0002414529484529221</v>
+        <v>-0.0001474611937832104</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.001363955643526959</v>
+        <v>-0.002383651081462543</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.002293397391311139</v>
+        <v>-0.001554008929593834</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0007109008236169251</v>
+        <v>-0.000259003514046377</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0005224711931934523</v>
+        <v>-0.0006003025467526263</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-2.877973906370013e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001582414846990804</v>
+        <v>-0.000546192875882312</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0005536036049585801</v>
+        <v>-0.0004525783595019012</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0002260995483563067</v>
+        <v>-0.0002406966261465582</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0008465777234674093</v>
+        <v>-0.001579516906543763</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0003298680527788978</v>
+        <v>-0.0007920518663128678</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0004611772267835878</v>
+        <v>-0.0009599692149097894</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-8.633921719110039e-05</v>
+        <v>1.046901172529202e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0.0001468285043070006</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-4.132016540181471e-05</v>
+        <v>-7.221053948812395e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0006111971118760662</v>
+        <v>-0.000849365007002703</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0</v>
+        <v>-0.0002306183600710971</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.001063898086808165</v>
+        <v>-0.001861487513311891</v>
       </c>
       <c r="EU6" t="n">
-        <v>-8.809710258420034e-05</v>
+        <v>-0.001101389427478616</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0.0001160541586073094</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.001066791996008057</v>
+        <v>-0.002125009834469152</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0002808988764044535</v>
+        <v>-0.0007624337511917545</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.001294886124105518</v>
+        <v>-0.0004935251686113585</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0006925740342160425</v>
+        <v>0.0004363738282104013</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004269006199782988</v>
+        <v>0.0003894875357899064</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002207417737681405</v>
+        <v>-0.0001615205110838902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001038469932468533</v>
+        <v>3.844994539609624e-05</v>
       </c>
       <c r="F7" t="n">
+        <v>-0.0006729803890839271</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0001571766316801282</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.0003332042704547289</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.0002523838468786899</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0001243698759594181</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.093802345057849e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.959275918985818e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.0001092539878723598</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.0008491710473109316</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.0001824944733688938</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.997600959613547e-05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0007544453835040931</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.001068102346672628</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.0003127172731928085</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0005820316434687722</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.0005522424180416873</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0002512562814070252</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0007483558734026342</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3.888024883359486e-05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.001498538998394378</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0004514094563233706</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.000305010773100528</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.699960254421434e-05</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.001024754171899966</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.004037619350916222</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.001472185691825734</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.0002717432786689566</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.0001465924792233841</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.0009689741333707203</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.0004626535793697372</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.01044745061942873</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.0001014010303086621</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0003617059544569147</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5.997600959612992e-05</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.0003358192506363266</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.0007134890757870993</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0006030331458778237</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.0006645488932875033</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.352658070801543e-05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.0004372178484246758</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.0003815531728735722</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.0006207655186772909</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.0004471489502869852</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.227228858835972e-05</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.0002184710208708585</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.0009612745800891331</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.0006264682850430636</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.003543990789378065</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.0003698201079355312</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.0001598231930693417</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.0001103748104732294</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.0002258425953018839</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.0007567775848354886</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.0003967768513813419</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.001166020749943586</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0004043671653862213</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.0005675807659054511</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.000447029141947175</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.001252099030315951</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.765346082246432e-05</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>6.636967530226586e-07</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.0006240751421055402</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.0006146972227090597</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0.0001220043092402257</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.0004931500483158658</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-0.0004997941931613293</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.0007914212730061154</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-0.000632239304298493</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.001123364279973238</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.0001244255321819487</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0.0001161334830854344</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0.0004703801438214583</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>-0.0007713086865873298</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0.0001696263990879299</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.0008791661745692625</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2.004668218699712e-05</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.001123554185665715</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.0004583813849696028</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-6.213753106874553e-05</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.0003029007059799415</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.0009118027304667153</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>4.174534762870219e-05</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>7.83668023055184e-05</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.000428800597946416</v>
+      </c>
+      <c r="CP7" t="n">
         <v>1.957713390759453e-05</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.001955316975637328</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0002594289953960605</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.001670880374093747</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0001978456855315558</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.000220744275860274</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0001238064925693227</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.002055323326017167</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0006593022311397133</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.0003825643216227526</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.559651385579457e-05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.0001839418327715725</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0008663536460273902</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.051515735817302e-05</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-6.488235307534063e-05</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.0002731889508692298</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.0008415737182294713</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.0001406645295485343</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.0001593381531527382</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.001132185538861374</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0004274002291880408</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.689535253789343e-05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.802707930368523e-05</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.002637589790559208</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.001970988088090409</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.001926765485558535</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.0001631553109711192</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.0002441027554925479</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0001726784343821896</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.0005937532951637569</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.01522102036662082</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.0003268586599054323</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.003521334616942501</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0008841752421554216</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.00231492522279399</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.0002978277370720539</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.0003614670785560992</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.001873504582185903</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.0001360808709175709</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-0.0001824034231960314</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.0002749211357447656</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.0006339424029383422</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.0001399440223910531</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.378718056136769e-05</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.0005424281206281245</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.0003629598930764977</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.003019027861104173</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.002466679290606344</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.0001360569797053735</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.000143190888705752</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.001118433681942244</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.002092454554906442</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.0003213130654945607</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-3.837298541828348e-05</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.001731652838999031</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0007421557489189601</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.0007319162140010605</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>2.080732417812925e-05</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-9.671179883946612e-05</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0.00325800957483216</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.0002335169620529043</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-2.476596290684752e-05</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>-0.0002384630240695906</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>-0.0001421055438636576</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>-0.0002981985144085819</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.0005423001314357412</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>9.593246354567265e-05</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.0008146936996539956</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.001722747914830952</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-0.0002530940959605432</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0002765402552473761</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.0006693563764783362</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>6.303958344606732e-05</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-0.0004385780111046733</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0.0003978399889406403</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.001108765577559068</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.0004156613178541269</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.001389301353840233</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>-0.0003719655442443293</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.460843976774373e-05</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.0002224019409623912</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>-8.205136489481956e-05</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.000124180248315664</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0.0004891746698171995</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>3.915426781518905e-05</v>
-      </c>
       <c r="CQ7" t="n">
-        <v>-0.001218345864473341</v>
+        <v>-0.0001662689657811467</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0007147336836603902</v>
+        <v>8.328696712383009e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0001773295816170306</v>
+        <v>-0.0004612570878856359</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.888024883361152e-05</v>
+        <v>0.0001830425113320766</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.0001208689327915569</v>
+        <v>-2.080732417810705e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>-5.859439223199758e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0003010118233337522</v>
+        <v>-0.0001050035660963511</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.000272668763977274</v>
+        <v>-0.0002322890248164788</v>
       </c>
       <c r="CZ7" t="n">
-        <v>5.755947812740026e-05</v>
+        <v>-6.281407035176877e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.093802345058404e-05</v>
+        <v>-0.0001413466586887735</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0.0001003721261652824</v>
+        <v>0.0001565439769673216</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0003676684910612238</v>
+        <v>0.0002303182579564578</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.051515735817857e-05</v>
+        <v>2.094679514034192e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0001542732240699896</v>
+        <v>6.242197253434335e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.000103221299911177</v>
+        <v>0.0005191152324498904</v>
       </c>
       <c r="DG7" t="n">
-        <v>4.323547982522103e-05</v>
+        <v>0.0003161382275593594</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0001183606191927311</v>
+        <v>-0.000355125956317659</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0004471554246087972</v>
+        <v>0.0001942087742821008</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.000194599415480573</v>
+        <v>-0.000135337314524081</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0003471322907180108</v>
+        <v>-0.000800744357340244</v>
       </c>
       <c r="DL7" t="n">
-        <v>6.13835116789585e-05</v>
+        <v>-6.268337107929179e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0009080158069896705</v>
+        <v>-0.0003328112764291569</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0003822251340317273</v>
+        <v>-0.0009125793691920681</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.001975716483750017</v>
+        <v>-0.001096319498825399</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.923950883604095e-05</v>
+        <v>-0.001288396648500634</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0</v>
+        <v>6.281407035175213e-05</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0004638904648411546</v>
+        <v>-0.0007008704086888362</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0002925609326875189</v>
+        <v>-0.0004459770266916407</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-7.736943907157289e-05</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-5.845738274116719e-05</v>
+        <v>-0.0001392235152335164</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.021838803791364e-05</v>
+        <v>0.0004285839787097623</v>
       </c>
       <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>-0.0007687028140013542</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>-0.0006676968993139076</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-8.055104895876575e-07</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0002247789666752986</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0.0004815994541937207</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-2.106872272307214e-05</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>-0.0001151189562548005</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>-0.0009202225186375535</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.0003351048637967258</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>-0.0005139262426795631</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.0001182145529353529</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>5.802707930367968e-05</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-1.944012441679743e-05</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0.0001255412998798222</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>-0.000991010079218424</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>-0.0005646263296528953</v>
+      </c>
+      <c r="EV7" t="n">
         <v>2.08073241781126e-05</v>
       </c>
-      <c r="EA7" t="n">
-        <v>-9.593246354566709e-05</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>-0.0001502698997147278</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>0.0001456512692467993</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>-0.0001935213623278198</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>-0.0001399440223910586</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>-0.0001367219804327024</v>
-      </c>
-      <c r="EH7" t="n">
-        <v>3.915426781518905e-05</v>
-      </c>
-      <c r="EI7" t="n">
-        <v>-0.000118598179894247</v>
-      </c>
-      <c r="EJ7" t="n">
-        <v>0.0002296647615940783</v>
-      </c>
-      <c r="EK7" t="n">
-        <v>-0.0002647879674596954</v>
-      </c>
-      <c r="EL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ7" t="n">
-        <v>-8.077383911427316e-05</v>
-      </c>
-      <c r="ER7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET7" t="n">
-        <v>-0.0004677254194254854</v>
-      </c>
-      <c r="EU7" t="n">
-        <v>0.0003754450917479779</v>
-      </c>
-      <c r="EV7" t="n">
-        <v>0</v>
-      </c>
       <c r="EW7" t="n">
-        <v>-0.0002121424892117807</v>
+        <v>-0.0004580604596768068</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0003155356877701243</v>
+        <v>-0.0002750549818445636</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0004221831850477753</v>
+        <v>-0.0002639726464803094</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003239257808720364</v>
+        <v>0.001377151316767211</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007393083987029203</v>
+        <v>0.0009281658629633981</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00108698043982092</v>
+        <v>0.000115118956254806</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001089593488117893</v>
+        <v>0.0004239064584437569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001918160708915317</v>
+        <v>-0.0004355316004124338</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002874438178046093</v>
+        <v>0.002603033153809287</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001049081422416587</v>
+        <v>0.0004341273331589845</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003878058786706324</v>
+        <v>0.001282091288029841</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001028211062453202</v>
+        <v>0.00108375470236689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003106607346904905</v>
+        <v>0.0002478426047315601</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002152799682381551</v>
+        <v>0.0001854206321972363</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000564869078652383</v>
+        <v>0.0008925261709731513</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003644331564724853</v>
+        <v>0.004450973100942298</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003249724254426398</v>
+        <v>0.0001254752114329349</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005409009982067697</v>
+        <v>0.001073302520577746</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005708467933077993</v>
+        <v>0.00543794613169695</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002877973906369929</v>
+        <v>9.490936127615757e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001282859290301422</v>
+        <v>0.0002716098630532154</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002784577759901069</v>
+        <v>2.936570086139456e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0006996196808399663</v>
+        <v>-1.934235976786547e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001502411184667291</v>
+        <v>0.001313699135418181</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001850181712810489</v>
+        <v>0.001560057106134571</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002921464425028789</v>
+        <v>0.0004445559638359436</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003115066915388931</v>
+        <v>3.142019271051288e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00352359680347587</v>
+        <v>0.001829385708519995</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003629541968389163</v>
+        <v>0.002582597614220597</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001069683408294409</v>
+        <v>0.0007068551410509994</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0006218124511594675</v>
+        <v>0.0006898180748558441</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.003941151515504562</v>
+        <v>0.005699453420409076</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.004948985792510663</v>
+        <v>0.004772386164459394</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003004601237489962</v>
+        <v>0.002971539916731891</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006022344693476401</v>
+        <v>0.0006340082922971502</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002690136531726589</v>
+        <v>0.0002912206102737291</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.000739407871076836</v>
+        <v>0.002895197240960107</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.007392319357751878</v>
+        <v>0.003099570894215933</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02075595472507989</v>
+        <v>0.01961380076966979</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0007246040410302328</v>
+        <v>0.0004916162984535344</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.006199168987026197</v>
+        <v>0.003843692702367363</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001937117168389907</v>
+        <v>0.0008451742474345575</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006719357924504743</v>
+        <v>0.00109122978582982</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0006150556839269795</v>
+        <v>8.273289903300285e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001804621881125518</v>
+        <v>0.001319516518495273</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01254080599334318</v>
+        <v>0.005716539504146542</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005118540090676832</v>
+        <v>0.0003082393898823366</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0006372940252246606</v>
+        <v>0.0003111597960658685</v>
       </c>
       <c r="AU8" t="n">
-        <v>-6.978002059415956e-05</v>
+        <v>0.0005665230019967187</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001031136271734723</v>
+        <v>0.001534581214055739</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007916408378404377</v>
+        <v>0.001547020353191567</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0002578822653593549</v>
+        <v>0.0001670531614160225</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0008612822203667187</v>
+        <v>0.001546375645549436</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002735291537406459</v>
+        <v>-2.856063967751065e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.006459923794046954</v>
+        <v>0.005595872343394462</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.005004213270249674</v>
+        <v>0.004395603899756662</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004120597705711187</v>
+        <v>-6.804043545878269e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002484182206514141</v>
+        <v>2.839929150220688e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002423789231906543</v>
+        <v>0.001015652753127208</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003417983731962404</v>
+        <v>0.002846322161204748</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.004885558908026497</v>
+        <v>0.002411956608936716</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0006321465672729011</v>
+        <v>0.001384663863847913</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01064358133164812</v>
+        <v>0.004434970546220796</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001450344520926056</v>
+        <v>0.002899362786595741</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.002150120385672605</v>
+        <v>0.0007102188138284281</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0006261233035564862</v>
+        <v>3.121098626717722e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001007345709240179</v>
+        <v>1.830389031873546e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.01067512909712033</v>
+        <v>0.002914300260806019</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002353718762266038</v>
+        <v>0.001103238847550547</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0004629010879501321</v>
+        <v>7.673793607304856e-05</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002942828721744306</v>
+        <v>0.003354293853509049</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001315676273882424</v>
+        <v>0.0005351237643619583</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0001007655264831514</v>
+        <v>0.001044556634911195</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001805601668210263</v>
+        <v>0.0001408900426428661</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001299789710786372</v>
+        <v>-0.0002426504455777079</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.916018662519615e-05</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.002132345560511659</v>
+        <v>-0.0002423844466273944</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.005055948464522356</v>
+        <v>0.0001549171654736003</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00104406843172008</v>
+        <v>0.001432666302452906</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0008114561329434</v>
+        <v>0.0001570351758793831</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001967849321970114</v>
+        <v>9.426057813153864e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0004423524247309463</v>
+        <v>-0.0002512762912175503</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0002508391507457158</v>
+        <v>0.0008905495626253728</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001164553755631603</v>
+        <v>0.001012196213811481</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001880509250214452</v>
+        <v>0.0002898212574266396</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001437140499605408</v>
+        <v>0.001854967647421579</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.003304515107877104</v>
+        <v>0.0009750606527214573</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.000489917255903885</v>
+        <v>0.0009786879621999673</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>2.901353965183983e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0006572514409571767</v>
+        <v>0.0007216184001251319</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.000673650313764268</v>
+        <v>0.003232402463699668</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0004468449903065858</v>
+        <v>0.0002593441628013893</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0003941699399000021</v>
+        <v>0.0007171858308840373</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.000667894982979847</v>
+        <v>0.0007230092473786532</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0001762732896051528</v>
+        <v>6.796314021645654e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0002794766690766476</v>
+        <v>0.0003191489361702466</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.003294310545087528</v>
+        <v>0.001444842035902172</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0008951318969899259</v>
+        <v>0.0007440694335457826</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001097149237407613</v>
+        <v>0.0005226786981673975</v>
       </c>
       <c r="CU8" t="n">
-        <v>-1.918649270913342e-05</v>
+        <v>0.0001352406513164927</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0002208982978627067</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>7.292044844524893e-05</v>
+        <v>0.0004314179515230277</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001210248824491644</v>
+        <v>0.0007584948914121092</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002471745543859676</v>
+        <v>0</v>
       </c>
       <c r="DA8" t="n">
-        <v>7.289537010450875e-05</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001646112056747556</v>
+        <v>0.001119784182389155</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0005857431736373459</v>
+        <v>0.0006448681838904541</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003935789210397333</v>
+        <v>0.000114144320053744</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0009154172588361792</v>
+        <v>0.0004887003208047468</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0005593999932418991</v>
+        <v>0.0007297366911928865</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003336410150113461</v>
+        <v>0.0004043206141453564</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0006591977956124456</v>
+        <v>0.000509752106907041</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001761275535833254</v>
+        <v>0.0005880619221143108</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001370528771384144</v>
+        <v>0.0009726032815277674</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.000186412593206256</v>
+        <v>-0.0002080622426988948</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.000204021163108678</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0.0002220445671525906</v>
+        <v>0.0002033100594447668</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0001353518244731622</v>
+        <v>0.0008472577144961106</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0001836864262637406</v>
+        <v>3.106876553439497e-05</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001482201986623882</v>
+        <v>-0.0003461262323575215</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>0.00011169512256817</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.065507480792486e-05</v>
+        <v>0.0001855133436747258</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0007322576786963963</v>
+        <v>2.877973906370013e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>9.511487551233099e-05</v>
+        <v>0.0002306285439427819</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0006906165042278395</v>
+        <v>0.0008843314372676214</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002334870072377731</v>
+        <v>6.838333448182521e-05</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0003745318352060267</v>
+        <v>0.0006231229469166738</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0009815321748372491</v>
+        <v>0.0026688063511564</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002199281914389534</v>
+        <v>3.90857630697905e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0006298381882678172</v>
+        <v>-0.0001244172828702733</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0007797057737480378</v>
+        <v>0.0005121922787092003</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0006155281518609446</v>
+        <v>0.0001658172252420959</v>
       </c>
       <c r="ED8" t="n">
-        <v>2.998800479804831e-05</v>
+        <v>0.0005756831982910881</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0002178088535245842</v>
+        <v>-0.000325849595944136</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0003032753740396243</v>
+        <v>0.00014346155484668</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002737182095401858</v>
+        <v>9.751401652569047e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.000572849591026356</v>
+        <v>-0.0003396700343944709</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003018014616781584</v>
+        <v>5.997600959614657e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>8.557198096643403e-05</v>
+        <v>0.0002517129688602737</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>3.032753740396243e-05</v>
+        <v>0.0002516950886048725</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0002842349475879246</v>
+        <v>0.0002358662286450069</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>2.998800479807329e-05</v>
+        <v>5.755947812740025e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0006206859298905354</v>
+        <v>1.942890293094024e-17</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>5.8027079303688e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0001368591047700929</v>
+        <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>-9.334851733593386e-05</v>
+        <v>-0.0003360306841506067</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0007147452061165683</v>
+        <v>5.755947812739748e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0001256807708420515</v>
+        <v>0.0002716629332221165</v>
       </c>
       <c r="EW8" t="n">
-        <v>-3.032753740396244e-05</v>
+        <v>0.000114973088487802</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0009074493938776796</v>
+        <v>-1.752264205848731e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>-8.748055987559399e-05</v>
+        <v>0.0001033154757378169</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006158357771261014</v>
+        <v>0.003620474406991303</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002359056377448976</v>
+        <v>0.001119552179128269</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002749696724625927</v>
+        <v>0.001498127340824007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001688411358403719</v>
+        <v>0.002033768227168076</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002021772939346822</v>
+        <v>8.378718056135659e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005794320798158126</v>
+        <v>0.008655846858094085</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001999200319872008</v>
+        <v>0.001466275659824057</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00853100291302542</v>
+        <v>0.004327923429047076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002760497667185125</v>
+        <v>0.001547388781431369</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001165210153974239</v>
+        <v>0.0005755947812740025</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00162297128589266</v>
+        <v>0.001044487427466167</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00259187620889747</v>
+        <v>0.001123595505618025</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006753645433614763</v>
+        <v>0.006783187682064151</v>
       </c>
       <c r="O9" t="n">
-        <v>0.007199334165626325</v>
+        <v>0.005243445692883953</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001340594888981961</v>
+        <v>0.00436953807740329</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02576455802262253</v>
+        <v>0.01478843736908255</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003868471953578323</v>
+        <v>0.002785299806576413</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003693623639191324</v>
+        <v>0.001414898044111579</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001040366208905563</v>
+        <v>0.0005832037325039119</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009593246354566709</v>
+        <v>0.001747815230961347</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004510108864696771</v>
+        <v>0.006065318818040455</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004528012279355354</v>
+        <v>0.004177949709864614</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008927173061863724</v>
+        <v>0.01061173533083649</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001885211562630906</v>
+        <v>0.0003094777562862916</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00917469627147045</v>
+        <v>0.0119148936170213</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01285887585928022</v>
+        <v>0.004528912252325168</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001498127340823985</v>
+        <v>0.001586073500967133</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003396684189243815</v>
+        <v>0.003329171868497749</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.006752931661949069</v>
+        <v>0.01339991677070331</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02022471910112362</v>
+        <v>0.01783286685325867</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.006277489004398196</v>
+        <v>0.003728529534981162</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0009635525764557951</v>
+        <v>0.003142019271051544</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.005613741097612058</v>
+        <v>0.002553191489361728</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.006200251361541675</v>
+        <v>0.01210986267166045</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01265186426476748</v>
+        <v>0.01093422706325932</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02971285892634209</v>
+        <v>0.02474549725920121</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00399079048349964</v>
+        <v>0.002682737169517902</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01431334622823982</v>
+        <v>0.01152804642166346</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.008127356514453277</v>
+        <v>0.0106117353308365</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.008848864526233357</v>
+        <v>0.009654598418643422</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002597402597402598</v>
+        <v>0.003249516441005829</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004411152725759493</v>
+        <v>0.001856866537717639</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01963214714114347</v>
+        <v>0.01703318672530985</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0009976976208749377</v>
+        <v>0.004286308780690873</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002099533437014012</v>
+        <v>0.003829787234042581</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0006213753106876219</v>
+        <v>0.001831044527673775</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002505873140172277</v>
+        <v>0.005160216396171491</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003558994197292042</v>
+        <v>0.002288805659592219</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0008739076154806846</v>
+        <v>0.000418935902806894</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.003073190456934871</v>
+        <v>0.004827299209321734</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02654941373534338</v>
+        <v>0.00665377176015477</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.03471524288107203</v>
+        <v>0.02244556113902845</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01252600915522267</v>
+        <v>0.03923785594639864</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0007490636704120312</v>
+        <v>0.001856866537717627</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0006220839813375178</v>
+        <v>0.0002931323283081766</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003287557220141524</v>
+        <v>0.003810264385692075</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.02855946398659965</v>
+        <v>0.01453098827470686</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01029013539651834</v>
+        <v>0.01310720268006696</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001040366208905574</v>
+        <v>0.002379125095932455</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02015081692501048</v>
+        <v>0.02568665377176018</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003287557220141546</v>
+        <v>0.005285060341240167</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005152911604524501</v>
+        <v>0.001819652244237846</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002527216174183522</v>
+        <v>0.002220360284876421</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.005069124423963145</v>
+        <v>0.0008123791102514821</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02935510887772193</v>
+        <v>0.03978224455611388</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.005067001675041849</v>
+        <v>0.00833682446585673</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001819652244237746</v>
+        <v>0.0006281407035175657</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00754084625052367</v>
+        <v>0.01448189762796508</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.01273565144532884</v>
+        <v>0.005534748231377506</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.00301633850020947</v>
+        <v>0.003454015813566436</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01026392961876831</v>
+        <v>0.002099533437014001</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.007331378299120228</v>
+        <v>0.002553191489361728</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.378718056136769e-05</v>
+        <v>3.998400639743105e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002681189777963977</v>
+        <v>0.0006700167504187337</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01126937578550481</v>
+        <v>0.01776288227901131</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01562630917469625</v>
+        <v>0.00332688588007739</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002052785923753642</v>
+        <v>0.003644742354419783</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003538102643856977</v>
+        <v>0.006367041198501899</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.009007121910347726</v>
+        <v>0.002321083172147043</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.02312526183493925</v>
+        <v>0.008936170212765982</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00458786936236395</v>
+        <v>0.001555209953343706</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.01181399245915374</v>
+        <v>0.001382488479262678</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002799377916018708</v>
+        <v>0.003620474406991314</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.006200251361541664</v>
+        <v>0.001622971285892683</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01638039379974863</v>
+        <v>0.007074490220557683</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0003639304488475492</v>
+        <v>0.0001675041876046723</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.004577611319184371</v>
+        <v>0.00190513219284606</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.005150753768844196</v>
+        <v>0.005443886097152406</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002527216174183544</v>
+        <v>0.002514506769825953</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001213782302270949</v>
+        <v>0.00150816925010474</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001765157329240263</v>
+        <v>0.001424382069543362</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0005755947812740025</v>
+        <v>0.000348162475822078</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.006493506493506496</v>
+        <v>0.003435274403016353</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.008417085427135651</v>
+        <v>0.002707930367504885</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.007917888563049836</v>
+        <v>0.002178466694595749</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.004273146208630096</v>
+        <v>0.002973199329983223</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>0.0006397441023589745</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.002429828236279852</v>
+        <v>0.001382488479262678</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.005067001675041849</v>
+        <v>0.001968174204355078</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.007956448911222758</v>
+        <v>0.002088974854932335</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.002890657729367418</v>
+        <v>7.776049766718973e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001496158511928813</v>
+        <v>0.0002332814930015692</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001927105152911601</v>
+        <v>0.003404255319148963</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001205287713841408</v>
+        <v>0.001121856866537741</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001591956430666097</v>
+        <v>0.0009704811969268867</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.002304147465437767</v>
+        <v>0.002387934645999179</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001046901172529291</v>
+        <v>0.002136573104315054</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.01860075408462504</v>
+        <v>0.0008442056792018704</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01185588604943443</v>
+        <v>0.004286308780690839</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.005697528278173425</v>
+        <v>0.00220557636287978</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.006912442396313367</v>
+        <v>0.002746615087040638</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.003578859758635067</v>
+        <v>0.0007350096711799092</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0009720062208398494</v>
+        <v>0.0008510638297872464</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0003770423125261657</v>
+        <v>0.001237911025145089</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002136573104315032</v>
+        <v>0.002723083368244661</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001248439450686678</v>
+        <v>0.008364544319600552</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.004577611319184371</v>
+        <v>0.003037869330004217</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0002513615416841142</v>
+        <v>0.0001534919416730673</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003453568687644015</v>
+        <v>0.000618955512572561</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.00203911776945489</v>
+        <v>0.0004448038819248823</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.00222036028487641</v>
+        <v>0.001955888472742462</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001214914118139898</v>
+        <v>0.004119850187265984</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0008825786646201372</v>
+        <v>0.0001248439450686756</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001591289782244543</v>
+        <v>0.006325426550145707</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.005160216396171457</v>
+        <v>0.005160216396171502</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0007674597083653367</v>
+        <v>0.0002913025384935763</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.004608294930875567</v>
+        <v>0.001842546063651551</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.00925848345203183</v>
+        <v>0.005111018014243851</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.009928780896522816</v>
+        <v>0.0004852405984634656</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.002806870548806029</v>
+        <v>0.001698342094621996</v>
       </c>
       <c r="EE9" t="n">
-        <v>3.868471953578645e-05</v>
+        <v>0.000566114031540732</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.002723083368244661</v>
+        <v>0.000248550124275071</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.005571847507331374</v>
+        <v>0.000799680127948732</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001089233347297858</v>
+        <v>0.0006242197253433668</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.004398826979472137</v>
+        <v>0.00188521156263094</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.004398826979472137</v>
+        <v>0.00299625468164797</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0007959782153330264</v>
+        <v>0.0006609642301710683</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0005443886097152295</v>
+        <v>3.998400639743105e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004608294930875223</v>
+        <v>0.0004608294930875445</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0009209516500384041</v>
+        <v>0.001151189562548005</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0007118927973199241</v>
+        <v>0.0004043671653862324</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001800670016750405</v>
+        <v>0.0007537688442211032</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>0.002288805659592208</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0003351487222454707</v>
+        <v>0.0006576402321083585</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0008553654743390648</v>
+        <v>0.001298157453936333</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.006367825722664444</v>
+        <v>0.001622971285892671</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0003094777562862694</v>
+        <v>0.0003598560575769017</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0005197920831666591</v>
+        <v>0.001716917922948047</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001266308518802806</v>
+        <v>0.004827299209321734</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0001664585934249008</v>
+        <v>0.000812379110251471</v>
       </c>
     </row>
   </sheetData>
